--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/olderyoungersister.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/olderyoungersister.xlsx
@@ -730,7 +730,7 @@
     <t xml:space="preserve">你才不是我真正的#brother2呢！！！</t>
   </si>
   <si>
-    <t xml:space="preserve">诶真的吗…！？
+    <t xml:space="preserve">咦，真的吗…！？
 那我出几个#brother2绝对能答对的简单问题吧！</t>
   </si>
   <si>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/olderyoungersister.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/olderyoungersister.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="olderyoungersister" sheetId="1" r:id="rId3"/>
+    <sheet name="olderyoungersister" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="152">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -565,7 +565,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">全問正解おめでとう。それじゃあお小遣い頂戴</t>
@@ -584,7 +584,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">♪</t>
@@ -619,7 +619,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">わぁ、本物の</t>
@@ -638,7 +638,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">みーつけた！</t>
@@ -658,7 +658,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">そっかぁ…</t>
@@ -677,7 +677,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">は本物の</t>
@@ -696,7 +696,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">じゃなかったんだね…</t>
@@ -704,163 +704,6 @@
   </si>
   <si>
     <t xml:space="preserve">I see... so you weren't my real #brother2 after all... </t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">有什么事，#brother2？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想让你换个发型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的♪这个发型适合我吗。#brother2？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#brother2？你真是我的#brother2吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘟嘟—答错了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你才不是我真正的#brother2呢！！！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咦，真的吗…！？
-那我出几个#brother2绝对能答对的简单问题吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">问题：对「年长的妹」的描述正确的是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有血缘关系的年幼的女性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有血缘关系的年长的女性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没有血缘关系的年幼的女性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没有血缘关系的年长的女性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没有正确答案</t>
-  </si>
-  <si>
-    <t xml:space="preserve">叮咚。不愧是我的#brother2！那就来回答下一个问题吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">问题：我在#brother2的房间里偷偷藏起来的东西是什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">应急零食</t>
-  </si>
-  <si>
-    <t xml:space="preserve">为#brother2做的充满爱意的盒饭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">为#brother2写的充满爱意的信</t>
-  </si>
-  <si>
-    <t xml:space="preserve">装满至今回忆的时间胶囊</t>
-  </si>
-  <si>
-    <t xml:space="preserve">菜刀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么都没有藏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">问题：最强的盾是什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">钢铁盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔法盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">红宝石盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">以太盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无敌盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妹的笑容</t>
-  </si>
-  <si>
-    <t xml:space="preserve">问题：我喜欢的波球是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">普通的波球</t>
-  </si>
-  <si>
-    <t xml:space="preserve">红波球</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪波球</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金属波球</t>
-  </si>
-  <si>
-    <t xml:space="preserve">波球王</t>
-  </si>
-  <si>
-    <t xml:space="preserve">天使波球</t>
-  </si>
-  <si>
-    <t xml:space="preserve">波球蜗牛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">流浪波球</t>
-  </si>
-  <si>
-    <t xml:space="preserve">问题：我最想要#brother2怎么样？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花好多时间跟我在一起</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永远在一起</t>
-  </si>
-  <si>
-    <t xml:space="preserve">绝对不背叛我</t>
-  </si>
-  <si>
-    <t xml:space="preserve">摸我的头</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骂我</t>
-  </si>
-  <si>
-    <t xml:space="preserve">给我无限的零花钱</t>
-  </si>
-  <si>
-    <t xml:space="preserve">叮咚。不愧是我的#brother2！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜答对了所有问题。那请给我零花钱吧#brother2♪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">给10000奥伦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现在没有这么多钱</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇，我找到我的亲#brother2了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是吗…#brother2并不是真正的#brother2呢…</t>
   </si>
 </sst>
 </file>
@@ -881,25 +724,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -945,7 +788,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -954,86 +797,86 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1047,13 +890,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1229,25 +1072,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K121"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.57" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,23 +1125,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1306,7 +1149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1314,12 +1157,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
@@ -1327,35 +1170,35 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" ht="13.8">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" ht="13.8">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" ht="13.8">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
-      <c r="H16" s="1">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="5" t="s">
@@ -1364,11 +1207,8 @@
       <c r="J16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K16" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
@@ -1378,14 +1218,14 @@
       <c r="I17" s="5"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" ht="13.8">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="1" t="n">
         <v>56</v>
       </c>
       <c r="I18" s="8" t="s">
@@ -1394,17 +1234,14 @@
       <c r="J18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G19" s="5"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1412,17 +1249,17 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1430,8 +1267,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
-      <c r="H26" s="1">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
         <v>57</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1440,28 +1277,25 @@
       <c r="J26" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K26" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="13.8">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
-      <c r="H30" s="1">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="10" t="s">
@@ -1470,21 +1304,18 @@
       <c r="J30" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K30" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" ht="13.8">
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I31" s="8"/>
     </row>
-    <row r="32" ht="13.8">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -1493,11 +1324,8 @@
       <c r="J32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K32" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1505,12 +1333,12 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -1521,8 +1349,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
-      <c r="H38" s="1">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I38" s="11" t="s">
@@ -1531,12 +1359,9 @@
       <c r="J38" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K38" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" ht="12.8">
-      <c r="H39" s="1">
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I39" s="11" t="s">
@@ -1545,36 +1370,33 @@
       <c r="J39" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="K39" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="40" ht="12.8">
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" ht="12.8">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="1"/>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I43" s="1"/>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" ht="43.25">
-      <c r="H45" s="1">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I45" s="5" t="s">
@@ -1583,12 +1405,9 @@
       <c r="J45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K45" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" ht="12.8">
-      <c r="H46" s="1">
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -1597,18 +1416,15 @@
       <c r="J46" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K46" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="47" ht="12.8">
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -1617,18 +1433,15 @@
       <c r="J47" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K47" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" ht="12.8">
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -1637,18 +1450,15 @@
       <c r="J48" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K48" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="49" ht="12.8">
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -1657,11 +1467,8 @@
       <c r="J49" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="K49" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="50" ht="12.8">
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
         <v>57</v>
       </c>
@@ -1669,7 +1476,7 @@
       <c r="D50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -1678,11 +1485,8 @@
       <c r="J50" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K50" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" ht="12.8">
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
         <v>39</v>
       </c>
@@ -1690,7 +1494,7 @@
       <c r="D51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -1699,23 +1503,20 @@
       <c r="J51" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K51" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="52" ht="12.8">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="1"/>
     </row>
-    <row r="53" ht="12.8">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="1"/>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" ht="15">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D55" s="13" t="s">
         <v>40</v>
       </c>
@@ -1724,8 +1525,8 @@
       </c>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" ht="12.8">
-      <c r="H56" s="1">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -1734,12 +1535,9 @@
       <c r="J56" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K56" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" ht="12.8">
-      <c r="H57" s="1">
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -1748,18 +1546,15 @@
       <c r="J57" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="K57" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" ht="12.8">
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -1768,18 +1563,15 @@
       <c r="J58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="K58" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" ht="12.8">
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -1788,18 +1580,15 @@
       <c r="J59" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K59" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" ht="12.8">
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H60" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -1808,18 +1597,15 @@
       <c r="J60" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K60" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="61" ht="12.8">
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -1828,18 +1614,15 @@
       <c r="J61" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="K61" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="62" ht="12.8">
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -1848,11 +1631,8 @@
       <c r="J62" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K62" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" ht="12.8">
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="5" t="s">
         <v>39</v>
       </c>
@@ -1860,7 +1640,7 @@
       <c r="D63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -1869,11 +1649,8 @@
       <c r="J63" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K63" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" ht="12.8">
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="5" t="s">
         <v>79</v>
       </c>
@@ -1881,7 +1658,7 @@
       <c r="D64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H64" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -1890,23 +1667,20 @@
       <c r="J64" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K64" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" ht="12.8">
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I65" s="1"/>
     </row>
-    <row r="66" ht="12.8">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I66" s="1"/>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" ht="15">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D68" s="13" t="s">
         <v>40</v>
       </c>
@@ -1915,8 +1689,8 @@
       </c>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" ht="12.8">
-      <c r="H69" s="1">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -1925,12 +1699,9 @@
       <c r="J69" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K69" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="70" ht="12.8">
-      <c r="H70" s="1">
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -1939,18 +1710,15 @@
       <c r="J70" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K70" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="71" ht="12.8">
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -1959,18 +1727,15 @@
       <c r="J71" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K71" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="72" ht="12.8">
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -1979,18 +1744,15 @@
       <c r="J72" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="K72" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="73" ht="12.8">
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H73" s="1">
+      <c r="H73" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -1999,18 +1761,15 @@
       <c r="J73" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="K73" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="74" ht="12.8">
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -2019,18 +1778,15 @@
       <c r="J74" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K74" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="75" ht="12.8">
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H75" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -2039,11 +1795,8 @@
       <c r="J75" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K75" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="76" ht="12.8">
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
         <v>94</v>
       </c>
@@ -2051,7 +1804,7 @@
       <c r="D76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -2060,20 +1813,17 @@
       <c r="J76" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="K76" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="77" ht="12.8">
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="1"/>
     </row>
-    <row r="78" ht="12.8">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>94</v>
       </c>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" ht="15">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D79" s="13" t="s">
         <v>40</v>
       </c>
@@ -2082,8 +1832,8 @@
       </c>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" ht="12.8">
-      <c r="H80" s="1">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -2092,12 +1842,9 @@
       <c r="J80" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K80" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="81" ht="12.8">
-      <c r="H81" s="1">
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H81" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -2106,18 +1853,15 @@
       <c r="J81" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="K81" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="82" ht="12.8">
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H82" s="1" t="n">
         <v>32</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -2126,18 +1870,15 @@
       <c r="J82" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K82" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="83" ht="12.8">
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H83" s="1">
+      <c r="H83" s="1" t="n">
         <v>33</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -2146,18 +1887,15 @@
       <c r="J83" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K83" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="84" ht="12.8">
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="1" t="s">
         <v>103</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H84" s="1" t="n">
         <v>34</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -2166,18 +1904,15 @@
       <c r="J84" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K84" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="85" ht="12.8">
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H85" s="1" t="n">
         <v>35</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -2186,18 +1921,15 @@
       <c r="J85" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K85" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="86" ht="12.8">
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H86" s="1" t="n">
         <v>36</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -2206,11 +1938,8 @@
       <c r="J86" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="K86" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="87" ht="12.8">
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="5" t="s">
         <v>39</v>
       </c>
@@ -2218,7 +1947,7 @@
       <c r="D87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H87" s="1" t="n">
         <v>37</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -2227,11 +1956,8 @@
       <c r="J87" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K87" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="88" ht="12.8">
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="5" t="s">
         <v>39</v>
       </c>
@@ -2239,7 +1965,7 @@
       <c r="D88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H88" s="1" t="n">
         <v>38</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -2248,11 +1974,8 @@
       <c r="J88" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K88" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="89" ht="12.8">
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="5" t="s">
         <v>39</v>
       </c>
@@ -2260,7 +1983,7 @@
       <c r="D89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H89" s="1" t="n">
         <v>39</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -2269,23 +1992,20 @@
       <c r="J89" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="K89" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="90" ht="12.8">
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I90" s="1"/>
     </row>
-    <row r="91" ht="12.8">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I91" s="1"/>
     </row>
-    <row r="92" ht="12.8">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>103</v>
       </c>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" ht="15">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D93" s="13" t="s">
         <v>40</v>
       </c>
@@ -2294,8 +2014,8 @@
       </c>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" ht="12.8">
-      <c r="H94" s="1">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H94" s="1" t="n">
         <v>40</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -2304,12 +2024,9 @@
       <c r="J94" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K94" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="95" ht="12.8">
-      <c r="H95" s="1">
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H95" s="1" t="n">
         <v>41</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -2318,18 +2035,15 @@
       <c r="J95" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="K95" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="96" ht="12.8">
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H96" s="1" t="n">
         <v>42</v>
       </c>
       <c r="I96" s="5" t="s">
@@ -2338,18 +2052,15 @@
       <c r="J96" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="K96" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="97" ht="12.8">
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H97" s="1" t="n">
         <v>43</v>
       </c>
       <c r="I97" s="5" t="s">
@@ -2358,18 +2069,15 @@
       <c r="J97" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="K97" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="98" ht="12.8">
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H98" s="1" t="n">
         <v>44</v>
       </c>
       <c r="I98" s="5" t="s">
@@ -2378,18 +2086,15 @@
       <c r="J98" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K98" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="99" ht="12.8">
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H99" s="1">
+      <c r="H99" s="1" t="n">
         <v>45</v>
       </c>
       <c r="I99" s="5" t="s">
@@ -2398,18 +2103,15 @@
       <c r="J99" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="K99" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="100" ht="12.8">
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H100" s="1">
+      <c r="H100" s="1" t="n">
         <v>46</v>
       </c>
       <c r="I100" s="5" t="s">
@@ -2418,18 +2120,15 @@
       <c r="J100" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K100" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="101" ht="12.8">
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H101" s="1">
+      <c r="H101" s="1" t="n">
         <v>47</v>
       </c>
       <c r="I101" s="5" t="s">
@@ -2438,11 +2137,8 @@
       <c r="J101" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="K101" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="102" ht="12.8">
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="5" t="s">
         <v>39</v>
       </c>
@@ -2450,7 +2146,7 @@
       <c r="D102" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H102" s="1">
+      <c r="H102" s="1" t="n">
         <v>48</v>
       </c>
       <c r="I102" s="1" t="s">
@@ -2459,11 +2155,8 @@
       <c r="J102" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="K102" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="103" ht="12.8">
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="5" t="s">
         <v>39</v>
       </c>
@@ -2471,7 +2164,7 @@
       <c r="D103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H103" s="1">
+      <c r="H103" s="1" t="n">
         <v>49</v>
       </c>
       <c r="I103" s="5" t="s">
@@ -2480,19 +2173,16 @@
       <c r="J103" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K103" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="104" ht="12.8">
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I104" s="1"/>
     </row>
-    <row r="106" ht="12.8">
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="107" ht="15">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="13" t="s">
         <v>40</v>
       </c>
@@ -2500,8 +2190,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" ht="12.8">
-      <c r="H108" s="1">
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H108" s="1" t="n">
         <v>50</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -2510,12 +2200,9 @@
       <c r="J108" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K108" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="109" ht="13.4">
-      <c r="H109" s="1">
+    </row>
+    <row r="109" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H109" s="1" t="n">
         <v>51</v>
       </c>
       <c r="I109" s="6" t="s">
@@ -2524,11 +2211,8 @@
       <c r="J109" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K109" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="110" ht="12.8">
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="1" t="s">
         <v>139</v>
       </c>
@@ -2538,7 +2222,7 @@
       <c r="D110" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H110" s="1">
+      <c r="H110" s="1" t="n">
         <v>52</v>
       </c>
       <c r="I110" s="2" t="s">
@@ -2547,18 +2231,15 @@
       <c r="J110" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K110" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="111" ht="12.8">
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H111" s="1">
+      <c r="H111" s="1" t="n">
         <v>53</v>
       </c>
       <c r="I111" s="2" t="s">
@@ -2567,17 +2248,14 @@
       <c r="J111" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K111" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="113" ht="12.8">
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="114" ht="13.4">
-      <c r="H114" s="1">
+    <row r="114" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H114" s="1" t="n">
         <v>54</v>
       </c>
       <c r="I114" s="6" t="s">
@@ -2586,11 +2264,8 @@
       <c r="J114" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K114" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="115" ht="22.35">
+    </row>
+    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="5" t="s">
         <v>17</v>
       </c>
@@ -2599,7 +2274,7 @@
       </c>
       <c r="I115" s="6"/>
     </row>
-    <row r="116" ht="12.8">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="1" t="s">
         <v>29</v>
       </c>
@@ -2607,18 +2282,18 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" ht="12.8">
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="119" ht="12.8">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="120" ht="12.8">
-      <c r="H120" s="1">
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H120" s="1" t="n">
         <v>55</v>
       </c>
       <c r="I120" s="6" t="s">
@@ -2627,23 +2302,20 @@
       <c r="J120" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="K120" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="121" ht="12.8">
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="1" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H21:H32 I33 H4:H18 I19:I20 H34:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/olderyoungersister.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/olderyoungersister.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="olderyoungersister" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="olderyoungersister" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="204">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -565,7 +565,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">全問正解おめでとう。それじゃあお小遣い頂戴</t>
@@ -584,7 +584,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">♪</t>
@@ -619,7 +619,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">わぁ、本物の</t>
@@ -638,7 +638,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">みーつけた！</t>
@@ -658,7 +658,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">そっかぁ…</t>
@@ -677,7 +677,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">は本物の</t>
@@ -696,7 +696,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">じゃなかったんだね…</t>
@@ -704,6 +704,163 @@
   </si>
   <si>
     <t xml:space="preserve">I see... so you weren't my real #brother2 after all... </t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">有什么事，#brother2？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想让你换个发型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的♪这个发型适合我吗。#brother2？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#brother2？你真是我的#brother2吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘟嘟—答错了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你才不是我真正的#brother2呢！！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咦，真的吗…！？
+那我出几个#brother2绝对能答对的简单问题吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">问题：对「年长的妹」的描述正确的是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有血缘关系的年幼的女性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有血缘关系的年长的女性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有血缘关系的年幼的女性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有血缘关系的年长的女性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有正确答案</t>
+  </si>
+  <si>
+    <t xml:space="preserve">叮咚。不愧是我的#brother2！那就来回答下一个问题吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">问题：我在#brother2的房间里偷偷藏起来的东西是什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">应急零食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">为#brother2做的充满爱意的盒饭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">为#brother2写的充满爱意的信</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装满至今回忆的时间胶囊</t>
+  </si>
+  <si>
+    <t xml:space="preserve">菜刀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么都没有藏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">问题：最强的盾是什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">钢铁盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔法盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">红宝石盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以太盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无敌盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妹的笑容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">问题：我喜欢的波球是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普通的波球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">红波球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪波球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金属波球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">波球王</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天使波球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">波球蜗牛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流浪波球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">问题：我最想要#brother2怎么样？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">花好多时间跟我在一起</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永远在一起</t>
+  </si>
+  <si>
+    <t xml:space="preserve">绝对不背叛我</t>
+  </si>
+  <si>
+    <t xml:space="preserve">摸我的头</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骂我</t>
+  </si>
+  <si>
+    <t xml:space="preserve">给我无限的零花钱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">叮咚。不愧是我的#brother2！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜答对了所有问题。那请给我零花钱吧#brother2♪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">给10000奥伦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在没有这么多钱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哇，我找到我的亲#brother2了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是吗…#brother2并不是真正的#brother2呢…</t>
   </si>
 </sst>
 </file>
@@ -724,25 +881,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -788,7 +945,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -797,86 +954,86 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -890,13 +1047,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1072,25 +1229,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K121"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
+    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.57" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1125,23 +1282,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1149,7 +1306,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1157,12 +1314,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
@@ -1170,35 +1327,35 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="13.8">
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="13.8">
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="13.8">
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="1" t="n">
+    <row r="16" ht="12.8">
+      <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="5" t="s">
@@ -1207,8 +1364,11 @@
       <c r="J16" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
@@ -1218,14 +1378,14 @@
       <c r="I17" s="5"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="13.8">
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="1">
         <v>56</v>
       </c>
       <c r="I18" s="8" t="s">
@@ -1234,14 +1394,17 @@
       <c r="J18" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="G19" s="5"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1249,17 +1412,17 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="D25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1267,8 +1430,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="1" t="n">
+    <row r="26" ht="12.8">
+      <c r="H26" s="1">
         <v>57</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1277,25 +1440,28 @@
       <c r="J26" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="13.8">
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H30" s="1" t="n">
+    <row r="30" ht="12.8">
+      <c r="H30" s="1">
         <v>2</v>
       </c>
       <c r="I30" s="10" t="s">
@@ -1304,18 +1470,21 @@
       <c r="J30" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" ht="13.8">
       <c r="I31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="13.8">
       <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="1">
         <v>3</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -1324,8 +1493,11 @@
       <c r="J32" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="D33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1333,12 +1505,12 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="D34" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -1349,8 +1521,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H38" s="1" t="n">
+    <row r="38" ht="12.8">
+      <c r="H38" s="1">
         <v>4</v>
       </c>
       <c r="I38" s="11" t="s">
@@ -1359,9 +1531,12 @@
       <c r="J38" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H39" s="1" t="n">
+      <c r="K38" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" ht="12.8">
+      <c r="H39" s="1">
         <v>5</v>
       </c>
       <c r="I39" s="11" t="s">
@@ -1370,33 +1545,36 @@
       <c r="J39" s="12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" ht="12.8">
       <c r="D40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="B41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="12.8">
       <c r="I42" s="1"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="I43" s="1"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="A44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H45" s="1" t="n">
+    <row r="45" ht="43.25">
+      <c r="H45" s="1">
         <v>6</v>
       </c>
       <c r="I45" s="5" t="s">
@@ -1405,9 +1583,12 @@
       <c r="J45" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H46" s="1" t="n">
+      <c r="K45" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" ht="12.8">
+      <c r="H46" s="1">
         <v>7</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -1416,15 +1597,18 @@
       <c r="J46" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K46" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" ht="12.8">
       <c r="B47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="1" t="n">
+      <c r="H47" s="1">
         <v>8</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -1433,15 +1617,18 @@
       <c r="J47" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K47" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" ht="12.8">
       <c r="B48" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H48" s="1" t="n">
+      <c r="H48" s="1">
         <v>9</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -1450,15 +1637,18 @@
       <c r="J48" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" ht="12.8">
       <c r="B49" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="H49" s="1">
         <v>10</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -1467,8 +1657,11 @@
       <c r="J49" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K49" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" ht="12.8">
       <c r="B50" s="5" t="s">
         <v>57</v>
       </c>
@@ -1476,7 +1669,7 @@
       <c r="D50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="H50" s="1">
         <v>11</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -1485,8 +1678,11 @@
       <c r="J50" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K50" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" ht="12.8">
       <c r="B51" s="5" t="s">
         <v>39</v>
       </c>
@@ -1494,7 +1690,7 @@
       <c r="D51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="1">
         <v>12</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -1503,20 +1699,23 @@
       <c r="J51" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K51" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" ht="12.8">
       <c r="I52" s="1"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.8">
       <c r="I53" s="1"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="15">
       <c r="D55" s="13" t="s">
         <v>40</v>
       </c>
@@ -1525,8 +1724,8 @@
       </c>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H56" s="1" t="n">
+    <row r="56" ht="12.8">
+      <c r="H56" s="1">
         <v>13</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -1535,9 +1734,12 @@
       <c r="J56" s="9" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H57" s="1" t="n">
+      <c r="K56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" ht="12.8">
+      <c r="H57" s="1">
         <v>14</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -1546,15 +1748,18 @@
       <c r="J57" s="12" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" ht="12.8">
       <c r="B58" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="1">
         <v>15</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -1563,15 +1768,18 @@
       <c r="J58" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K58" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="59" ht="12.8">
       <c r="B59" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="1">
         <v>16</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -1580,15 +1788,18 @@
       <c r="J59" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" ht="12.8">
       <c r="B60" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="H60" s="1">
         <v>17</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -1597,15 +1808,18 @@
       <c r="J60" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" ht="12.8">
       <c r="B61" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="1" t="n">
+      <c r="H61" s="1">
         <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -1614,15 +1828,18 @@
       <c r="J61" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" ht="12.8">
       <c r="B62" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="H62" s="1">
         <v>19</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -1631,8 +1848,11 @@
       <c r="J62" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" ht="12.8">
       <c r="B63" s="5" t="s">
         <v>39</v>
       </c>
@@ -1640,7 +1860,7 @@
       <c r="D63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="1" t="n">
+      <c r="H63" s="1">
         <v>20</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -1649,8 +1869,11 @@
       <c r="J63" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K63" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" ht="12.8">
       <c r="B64" s="5" t="s">
         <v>79</v>
       </c>
@@ -1658,7 +1881,7 @@
       <c r="D64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="H64" s="1">
         <v>21</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -1667,20 +1890,23 @@
       <c r="J64" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K64" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" ht="12.8">
       <c r="I65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="12.8">
       <c r="I66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
       <c r="A67" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" ht="15">
       <c r="D68" s="13" t="s">
         <v>40</v>
       </c>
@@ -1689,8 +1915,8 @@
       </c>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H69" s="1" t="n">
+    <row r="69" ht="12.8">
+      <c r="H69" s="1">
         <v>22</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -1699,9 +1925,12 @@
       <c r="J69" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H70" s="1" t="n">
+      <c r="K69" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" ht="12.8">
+      <c r="H70" s="1">
         <v>23</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -1710,15 +1939,18 @@
       <c r="J70" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K70" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="71" ht="12.8">
       <c r="B71" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="H71" s="1">
         <v>24</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -1727,15 +1959,18 @@
       <c r="J71" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K71" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" ht="12.8">
       <c r="B72" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H72" s="1" t="n">
+      <c r="H72" s="1">
         <v>25</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -1744,15 +1979,18 @@
       <c r="J72" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K72" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="73" ht="12.8">
       <c r="B73" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="H73" s="1">
         <v>26</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -1761,15 +1999,18 @@
       <c r="J73" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K73" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" ht="12.8">
       <c r="B74" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="H74" s="1">
         <v>27</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -1778,15 +2019,18 @@
       <c r="J74" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" ht="12.8">
       <c r="B75" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="H75" s="1">
         <v>28</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -1795,8 +2039,11 @@
       <c r="J75" s="5" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K75" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" ht="12.8">
       <c r="B76" s="1" t="s">
         <v>94</v>
       </c>
@@ -1804,7 +2051,7 @@
       <c r="D76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="H76" s="1">
         <v>29</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -1813,17 +2060,20 @@
       <c r="J76" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" ht="12.8">
       <c r="I77" s="1"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.8">
       <c r="A78" s="1" t="s">
         <v>94</v>
       </c>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="15">
       <c r="D79" s="13" t="s">
         <v>40</v>
       </c>
@@ -1832,8 +2082,8 @@
       </c>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="1" t="n">
+    <row r="80" ht="12.8">
+      <c r="H80" s="1">
         <v>30</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -1842,9 +2092,12 @@
       <c r="J80" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H81" s="1" t="n">
+      <c r="K80" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="81" ht="12.8">
+      <c r="H81" s="1">
         <v>31</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -1853,15 +2106,18 @@
       <c r="J81" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K81" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="82" ht="12.8">
       <c r="B82" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="H82" s="1">
         <v>32</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -1870,15 +2126,18 @@
       <c r="J82" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" ht="12.8">
       <c r="B83" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H83" s="1" t="n">
+      <c r="H83" s="1">
         <v>33</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -1887,15 +2146,18 @@
       <c r="J83" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K83" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" ht="12.8">
       <c r="B84" s="1" t="s">
         <v>103</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H84" s="1" t="n">
+      <c r="H84" s="1">
         <v>34</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -1904,15 +2166,18 @@
       <c r="J84" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K84" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="85" ht="12.8">
       <c r="B85" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H85" s="1" t="n">
+      <c r="H85" s="1">
         <v>35</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -1921,15 +2186,18 @@
       <c r="J85" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K85" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="86" ht="12.8">
       <c r="B86" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="H86" s="1">
         <v>36</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -1938,8 +2206,11 @@
       <c r="J86" s="5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K86" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="87" ht="12.8">
       <c r="B87" s="5" t="s">
         <v>39</v>
       </c>
@@ -1947,7 +2218,7 @@
       <c r="D87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H87" s="1" t="n">
+      <c r="H87" s="1">
         <v>37</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -1956,8 +2227,11 @@
       <c r="J87" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K87" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="88" ht="12.8">
       <c r="B88" s="5" t="s">
         <v>39</v>
       </c>
@@ -1965,7 +2239,7 @@
       <c r="D88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H88" s="1" t="n">
+      <c r="H88" s="1">
         <v>38</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -1974,8 +2248,11 @@
       <c r="J88" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K88" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="89" ht="12.8">
       <c r="B89" s="5" t="s">
         <v>39</v>
       </c>
@@ -1983,7 +2260,7 @@
       <c r="D89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H89" s="1" t="n">
+      <c r="H89" s="1">
         <v>39</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -1992,20 +2269,23 @@
       <c r="J89" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K89" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" ht="12.8">
       <c r="I90" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.8">
       <c r="I91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.8">
       <c r="A92" s="1" t="s">
         <v>103</v>
       </c>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="15">
       <c r="D93" s="13" t="s">
         <v>40</v>
       </c>
@@ -2014,8 +2294,8 @@
       </c>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H94" s="1" t="n">
+    <row r="94" ht="12.8">
+      <c r="H94" s="1">
         <v>40</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -2024,9 +2304,12 @@
       <c r="J94" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H95" s="1" t="n">
+      <c r="K94" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="95" ht="12.8">
+      <c r="H95" s="1">
         <v>41</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -2035,15 +2318,18 @@
       <c r="J95" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K95" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="96" ht="12.8">
       <c r="B96" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="H96" s="1">
         <v>42</v>
       </c>
       <c r="I96" s="5" t="s">
@@ -2052,15 +2338,18 @@
       <c r="J96" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K96" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97" ht="12.8">
       <c r="B97" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="H97" s="1">
         <v>43</v>
       </c>
       <c r="I97" s="5" t="s">
@@ -2069,15 +2358,18 @@
       <c r="J97" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K97" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" ht="12.8">
       <c r="B98" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H98" s="1" t="n">
+      <c r="H98" s="1">
         <v>44</v>
       </c>
       <c r="I98" s="5" t="s">
@@ -2086,15 +2378,18 @@
       <c r="J98" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K98" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" ht="12.8">
       <c r="B99" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H99" s="1" t="n">
+      <c r="H99" s="1">
         <v>45</v>
       </c>
       <c r="I99" s="5" t="s">
@@ -2103,15 +2398,18 @@
       <c r="J99" s="5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K99" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="100" ht="12.8">
       <c r="B100" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H100" s="1" t="n">
+      <c r="H100" s="1">
         <v>46</v>
       </c>
       <c r="I100" s="5" t="s">
@@ -2120,15 +2418,18 @@
       <c r="J100" s="5" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K100" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="101" ht="12.8">
       <c r="B101" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H101" s="1" t="n">
+      <c r="H101" s="1">
         <v>47</v>
       </c>
       <c r="I101" s="5" t="s">
@@ -2137,8 +2438,11 @@
       <c r="J101" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K101" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" ht="12.8">
       <c r="B102" s="5" t="s">
         <v>39</v>
       </c>
@@ -2146,7 +2450,7 @@
       <c r="D102" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="H102" s="1">
         <v>48</v>
       </c>
       <c r="I102" s="1" t="s">
@@ -2155,8 +2459,11 @@
       <c r="J102" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K102" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" ht="12.8">
       <c r="B103" s="5" t="s">
         <v>39</v>
       </c>
@@ -2164,7 +2471,7 @@
       <c r="D103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="H103" s="1">
         <v>49</v>
       </c>
       <c r="I103" s="5" t="s">
@@ -2173,16 +2480,19 @@
       <c r="J103" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K103" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="104" ht="12.8">
       <c r="I104" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" ht="12.8">
       <c r="A106" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="15">
       <c r="D107" s="13" t="s">
         <v>40</v>
       </c>
@@ -2190,8 +2500,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H108" s="1" t="n">
+    <row r="108" ht="12.8">
+      <c r="H108" s="1">
         <v>50</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -2200,9 +2510,12 @@
       <c r="J108" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H109" s="1" t="n">
+      <c r="K108" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109" ht="13.4">
+      <c r="H109" s="1">
         <v>51</v>
       </c>
       <c r="I109" s="6" t="s">
@@ -2211,8 +2524,11 @@
       <c r="J109" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K109" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="110" ht="12.8">
       <c r="B110" s="1" t="s">
         <v>139</v>
       </c>
@@ -2222,7 +2538,7 @@
       <c r="D110" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H110" s="1" t="n">
+      <c r="H110" s="1">
         <v>52</v>
       </c>
       <c r="I110" s="2" t="s">
@@ -2231,15 +2547,18 @@
       <c r="J110" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K110" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" ht="12.8">
       <c r="B111" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="H111" s="1">
         <v>53</v>
       </c>
       <c r="I111" s="2" t="s">
@@ -2248,14 +2567,17 @@
       <c r="J111" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K111" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="113" ht="12.8">
       <c r="A113" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H114" s="1" t="n">
+    <row r="114" ht="13.4">
+      <c r="H114" s="1">
         <v>54</v>
       </c>
       <c r="I114" s="6" t="s">
@@ -2264,8 +2586,11 @@
       <c r="J114" s="9" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K114" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="115" ht="22.35">
       <c r="D115" s="5" t="s">
         <v>17</v>
       </c>
@@ -2274,7 +2599,7 @@
       </c>
       <c r="I115" s="6"/>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="12.8">
       <c r="D116" s="1" t="s">
         <v>29</v>
       </c>
@@ -2282,18 +2607,18 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" ht="12.8">
       <c r="B118" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" ht="12.8">
       <c r="A119" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H120" s="1" t="n">
+    <row r="120" ht="12.8">
+      <c r="H120" s="1">
         <v>55</v>
       </c>
       <c r="I120" s="6" t="s">
@@ -2302,20 +2627,23 @@
       <c r="J120" s="9" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K120" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="121" ht="12.8">
       <c r="B121" s="1" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H21:H32 I33 H4:H18 I19:I20 H34:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
